--- a/Apex Bank GRC Risk Register .xlsx
+++ b/Apex Bank GRC Risk Register .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laolu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{232C6A0D-B2F2-4A1A-B859-4A8C8E8D96AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C81476C2-4CCA-4502-8F8D-5B198B4FE6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read me" sheetId="5" r:id="rId1"/>
@@ -62,22 +62,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>5 x 5 risk heat map (Likelihood x Impact)</t>
-  </si>
-  <si>
     <t>Impact -&gt;</t>
   </si>
   <si>
     <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Bands:  Green 1-6 (low)   Amber 7-14 (medium)   Red 15-25 (priority)</t>
-  </si>
-  <si>
-    <t>Likelihood scale:  1 Rare   2 Unlikely   3 Possible   4 Likely   5 Almost certain</t>
-  </si>
-  <si>
-    <t>Impact scale:      1 Negligible   2 Minor   3 Moderate   4 Major   5 Severe</t>
   </si>
   <si>
     <t>Risk ID</t>
@@ -549,12 +537,24 @@
       <t>Cybersecurity (EDR, MFA, Malware), Infrastructure (DR/BCP, ATM uptime), Compliance (CBN/NDIC reporting automation), and Physical Access.</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">Likelihood scale:  1 Rare   2 Unlikely   3 Possible   4 Likely   </t>
+  </si>
+  <si>
+    <t>4 x 5 Risk Heat Map (Likelihood x Impact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact scale:  1 Negligible   2 Minor   3 Moderate   4 Major  5 Severe </t>
+  </si>
+  <si>
+    <t>Bands:  Green 1-6 (low)   Amber 7-12 (medium)   Red 13-20 (priority)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,12 +575,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FF145F88"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF1A80B6"/>
       <name val="Calibri"/>
@@ -594,12 +588,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1C1C1E"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -666,6 +654,13 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF1C1C1E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF145F88"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -780,21 +775,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -806,7 +799,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -824,22 +817,24 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1154,45 +1149,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:2" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B2" s="22" t="s">
-        <v>141</v>
+      <c r="B2" s="20" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>142</v>
+      <c r="B4" s="25" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
-        <v>143</v>
+      <c r="B6" s="27" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="28" t="s">
-        <v>144</v>
+      <c r="B7" s="26" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="28"/>
+      <c r="B8" s="26"/>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="28"/>
+      <c r="B9" s="26"/>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="28"/>
+      <c r="B10" s="26"/>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="28"/>
+      <c r="B11" s="26"/>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="28"/>
+      <c r="B12" s="26"/>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="28"/>
+      <c r="B13" s="26"/>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="28"/>
+      <c r="B14" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1230,1055 +1225,1055 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="14"/>
+    </row>
+    <row r="2" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="12">
+        <v>4</v>
+      </c>
+      <c r="G2" s="12">
+        <v>5</v>
+      </c>
+      <c r="H2" s="17">
+        <v>20</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="19">
+        <v>2</v>
+      </c>
+      <c r="M2" s="19">
+        <v>2</v>
+      </c>
+      <c r="N2" s="19">
+        <v>4</v>
+      </c>
+      <c r="O2" s="15">
+        <v>46265</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>46252</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="12">
+        <v>3</v>
+      </c>
+      <c r="G3" s="12">
+        <v>5</v>
+      </c>
+      <c r="H3" s="17">
+        <v>15</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="19">
+        <v>2</v>
+      </c>
+      <c r="M3" s="19">
+        <v>2</v>
+      </c>
+      <c r="N3" s="19">
+        <v>4</v>
+      </c>
+      <c r="O3" s="16">
+        <v>46264</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>46252</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="12">
+        <v>4</v>
+      </c>
+      <c r="G4" s="12">
+        <v>4</v>
+      </c>
+      <c r="H4" s="17">
+        <v>16</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="19">
+        <v>1</v>
+      </c>
+      <c r="M4" s="19">
+        <v>2</v>
+      </c>
+      <c r="N4" s="19">
+        <v>2</v>
+      </c>
+      <c r="O4" s="16">
+        <v>46264</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>46252</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="12">
+        <v>4</v>
+      </c>
+      <c r="G5" s="12">
+        <v>5</v>
+      </c>
+      <c r="H5" s="17">
+        <v>20</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5" s="19">
+        <v>1</v>
+      </c>
+      <c r="M5" s="19">
+        <v>2</v>
+      </c>
+      <c r="N5" s="19">
+        <v>2</v>
+      </c>
+      <c r="O5" s="16">
+        <v>46264</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>46252</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="12">
+        <v>4</v>
+      </c>
+      <c r="G6" s="12">
+        <v>5</v>
+      </c>
+      <c r="H6" s="17">
+        <v>20</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" s="19">
+        <v>1</v>
+      </c>
+      <c r="M6" s="19">
+        <v>2</v>
+      </c>
+      <c r="N6" s="19">
+        <v>2</v>
+      </c>
+      <c r="O6" s="16">
+        <v>46264</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>46252</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="C7" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="12">
+        <v>4</v>
+      </c>
+      <c r="G7" s="12">
+        <v>4</v>
+      </c>
+      <c r="H7" s="17">
+        <v>16</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="19">
+        <v>1</v>
+      </c>
+      <c r="M7" s="19">
+        <v>3</v>
+      </c>
+      <c r="N7" s="19">
+        <v>3</v>
+      </c>
+      <c r="O7" s="16">
+        <v>46280</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>46257</v>
+      </c>
+      <c r="R7" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="12">
+        <v>4</v>
+      </c>
+      <c r="G8" s="12">
+        <v>4</v>
+      </c>
+      <c r="H8" s="17">
+        <v>16</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="19">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="M8" s="19">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="12" t="s">
+      <c r="N8" s="19">
+        <v>6</v>
+      </c>
+      <c r="O8" s="16">
+        <v>46280</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>46257</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="12">
         <v>4</v>
       </c>
-      <c r="H1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="12" t="s">
+      <c r="G9" s="12">
         <v>5</v>
       </c>
-      <c r="J1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="O1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P1" s="12" t="s">
+      <c r="H9" s="17">
         <v>20</v>
       </c>
-      <c r="Q1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="16"/>
-    </row>
-    <row r="2" spans="1:19" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="I9" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" s="19">
+        <v>1</v>
+      </c>
+      <c r="M9" s="19">
+        <v>2</v>
+      </c>
+      <c r="N9" s="19">
+        <v>2</v>
+      </c>
+      <c r="O9" s="16">
+        <v>46280</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>46257</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="12">
+        <v>3</v>
+      </c>
+      <c r="G10" s="12">
+        <v>4</v>
+      </c>
+      <c r="H10" s="18">
+        <v>12</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="19">
+        <v>1</v>
+      </c>
+      <c r="M10" s="19">
+        <v>2</v>
+      </c>
+      <c r="N10" s="19">
+        <v>2</v>
+      </c>
+      <c r="O10" s="16">
+        <v>46280</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>46257</v>
+      </c>
+      <c r="R10" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="14">
+      <c r="D11" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="12">
         <v>4</v>
       </c>
-      <c r="G2" s="14">
-        <v>5</v>
-      </c>
-      <c r="H2" s="19">
-        <v>20</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" s="21">
+      <c r="G11" s="12">
+        <v>4</v>
+      </c>
+      <c r="H11" s="17">
+        <v>16</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="L11" s="19">
         <v>2</v>
       </c>
-      <c r="M2" s="21">
-        <v>2</v>
-      </c>
-      <c r="N2" s="21">
-        <v>4</v>
-      </c>
-      <c r="O2" s="17">
-        <v>46265</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="18">
-        <v>46252</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" s="14">
+      <c r="M11" s="19">
         <v>3</v>
       </c>
-      <c r="G3" s="14">
-        <v>5</v>
-      </c>
-      <c r="H3" s="19">
-        <v>15</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3" s="21">
-        <v>2</v>
-      </c>
-      <c r="M3" s="21">
-        <v>2</v>
-      </c>
-      <c r="N3" s="21">
-        <v>4</v>
-      </c>
-      <c r="O3" s="18">
-        <v>46264</v>
-      </c>
-      <c r="P3" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="18">
-        <v>46252</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="14">
-        <v>4</v>
-      </c>
-      <c r="G4" s="14">
-        <v>4</v>
-      </c>
-      <c r="H4" s="19">
-        <v>16</v>
-      </c>
-      <c r="I4" s="14" t="s">
+      <c r="N11" s="19">
+        <v>6</v>
+      </c>
+      <c r="O11" s="16">
+        <v>46280</v>
+      </c>
+      <c r="P11" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" s="21">
-        <v>1</v>
-      </c>
-      <c r="M4" s="21">
-        <v>2</v>
-      </c>
-      <c r="N4" s="21">
-        <v>2</v>
-      </c>
-      <c r="O4" s="18">
-        <v>46264</v>
-      </c>
-      <c r="P4" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q4" s="18">
-        <v>46252</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="14">
-        <v>4</v>
-      </c>
-      <c r="G5" s="14">
-        <v>5</v>
-      </c>
-      <c r="H5" s="19">
-        <v>20</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="L5" s="21">
-        <v>1</v>
-      </c>
-      <c r="M5" s="21">
-        <v>2</v>
-      </c>
-      <c r="N5" s="21">
-        <v>2</v>
-      </c>
-      <c r="O5" s="18">
-        <v>46264</v>
-      </c>
-      <c r="P5" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q5" s="18">
-        <v>46252</v>
-      </c>
-      <c r="R5" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="14">
-        <v>4</v>
-      </c>
-      <c r="G6" s="14">
-        <v>5</v>
-      </c>
-      <c r="H6" s="19">
-        <v>20</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L6" s="21">
-        <v>1</v>
-      </c>
-      <c r="M6" s="21">
-        <v>2</v>
-      </c>
-      <c r="N6" s="21">
-        <v>2</v>
-      </c>
-      <c r="O6" s="18">
-        <v>46264</v>
-      </c>
-      <c r="P6" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q6" s="18">
-        <v>46252</v>
-      </c>
-      <c r="R6" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="14">
-        <v>4</v>
-      </c>
-      <c r="G7" s="14">
-        <v>4</v>
-      </c>
-      <c r="H7" s="19">
-        <v>16</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="21">
-        <v>1</v>
-      </c>
-      <c r="M7" s="21">
-        <v>3</v>
-      </c>
-      <c r="N7" s="21">
-        <v>3</v>
-      </c>
-      <c r="O7" s="18">
-        <v>46280</v>
-      </c>
-      <c r="P7" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="18">
+      <c r="Q11" s="16">
         <v>46257</v>
       </c>
-      <c r="R7" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="14">
-        <v>4</v>
-      </c>
-      <c r="G8" s="14">
-        <v>4</v>
-      </c>
-      <c r="H8" s="19">
-        <v>16</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="21">
-        <v>2</v>
-      </c>
-      <c r="M8" s="21">
-        <v>3</v>
-      </c>
-      <c r="N8" s="21">
-        <v>6</v>
-      </c>
-      <c r="O8" s="18">
-        <v>46280</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>46257</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="14">
-        <v>4</v>
-      </c>
-      <c r="G9" s="14">
-        <v>5</v>
-      </c>
-      <c r="H9" s="19">
-        <v>20</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="L9" s="21">
-        <v>1</v>
-      </c>
-      <c r="M9" s="21">
-        <v>2</v>
-      </c>
-      <c r="N9" s="21">
-        <v>2</v>
-      </c>
-      <c r="O9" s="18">
-        <v>46280</v>
-      </c>
-      <c r="P9" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>46257</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="14">
-        <v>3</v>
-      </c>
-      <c r="G10" s="14">
-        <v>4</v>
-      </c>
-      <c r="H10" s="19">
-        <v>12</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="L10" s="21">
-        <v>1</v>
-      </c>
-      <c r="M10" s="21">
-        <v>2</v>
-      </c>
-      <c r="N10" s="21">
-        <v>2</v>
-      </c>
-      <c r="O10" s="18">
-        <v>46280</v>
-      </c>
-      <c r="P10" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>46257</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="14" t="s">
+      <c r="R11" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="14">
-        <v>4</v>
-      </c>
-      <c r="G11" s="14">
-        <v>4</v>
-      </c>
-      <c r="H11" s="19">
-        <v>16</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="21">
-        <v>2</v>
-      </c>
-      <c r="M11" s="21">
-        <v>3</v>
-      </c>
-      <c r="N11" s="21">
-        <v>6</v>
-      </c>
-      <c r="O11" s="18">
-        <v>46280</v>
-      </c>
-      <c r="P11" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>46257</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="13"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="11"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="13"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="11"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="13"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="11"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="13"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="11"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="13"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="11"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="13"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="11"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="13"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="11"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="13"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="11"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="13"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="11"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2288,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:G16"/>
+  <dimension ref="A2:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2296,151 +2291,131 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>2</v>
+      </c>
+      <c r="E5" s="6">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C5" s="7">
+      <c r="B6" s="6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>4</v>
+      </c>
+      <c r="D6" s="8">
+        <v>8</v>
+      </c>
+      <c r="E6" s="8">
+        <v>12</v>
+      </c>
+      <c r="F6" s="9">
+        <v>16</v>
+      </c>
+      <c r="G6" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8">
+        <v>9</v>
+      </c>
+      <c r="F7" s="8">
+        <v>12</v>
+      </c>
+      <c r="G7" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="6">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>4</v>
+      </c>
+      <c r="E8" s="7">
+        <v>6</v>
+      </c>
+      <c r="F8" s="8">
+        <v>8</v>
+      </c>
+      <c r="G8" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="7">
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
         <v>2</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E9" s="7">
         <v>3</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F9" s="7">
         <v>4</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G9" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="7">
-        <v>5</v>
-      </c>
-      <c r="C6" s="8">
-        <v>5</v>
-      </c>
-      <c r="D6" s="9">
-        <v>10</v>
-      </c>
-      <c r="E6" s="10">
-        <v>15</v>
-      </c>
-      <c r="F6" s="10">
-        <v>20</v>
-      </c>
-      <c r="G6" s="10">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="7">
-        <v>4</v>
-      </c>
-      <c r="C7" s="8">
-        <v>4</v>
-      </c>
-      <c r="D7" s="9">
-        <v>8</v>
-      </c>
-      <c r="E7" s="9">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10">
-        <v>16</v>
-      </c>
-      <c r="G7" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="7">
-        <v>3</v>
-      </c>
-      <c r="C8" s="8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="8">
-        <v>6</v>
-      </c>
-      <c r="E8" s="9">
-        <v>9</v>
-      </c>
-      <c r="F8" s="9">
-        <v>12</v>
-      </c>
-      <c r="G8" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="7">
-        <v>2</v>
-      </c>
-      <c r="C9" s="8">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8">
-        <v>4</v>
-      </c>
-      <c r="E9" s="8">
-        <v>6</v>
-      </c>
-      <c r="F9" s="9">
-        <v>8</v>
-      </c>
-      <c r="G9" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="7">
-        <v>1</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3</v>
-      </c>
-      <c r="F10" s="8">
-        <v>4</v>
-      </c>
-      <c r="G10" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="11" t="s">
-        <v>11</v>
-      </c>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
+      <c r="B14" s="26" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>13</v>
+      <c r="B15" s="26" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2462,255 +2437,255 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="17">
+      <c r="D2" s="15">
         <v>46265</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="16">
+        <v>46264</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="16">
+        <v>46264</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="18">
+      <c r="D5" s="16">
         <v>46264</v>
       </c>
-      <c r="E3" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="24" t="s">
+      <c r="E5" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G5" s="22" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+    <row r="6" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="16">
+        <v>46264</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="16">
+        <v>46280</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="18">
-        <v>46264</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="B8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="16">
+        <v>46280</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="18">
-        <v>46264</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="B9" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="16">
+        <v>46280</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="18">
-        <v>46264</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="B10" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="16">
+        <v>46280</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="18">
+      <c r="B11" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="16">
         <v>46280</v>
       </c>
-      <c r="E7" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="18">
-        <v>46280</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="18">
-        <v>46280</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="24" t="s">
+      <c r="E11" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G11" s="22" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="18">
-        <v>46280</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="18">
-        <v>46280</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
